--- a/Design Files/IoT-Speaker-v1.3/BOM/JLCPCB BOM-IoT-Speaker-v1.3.xlsx
+++ b/Design Files/IoT-Speaker-v1.3/BOM/JLCPCB BOM-IoT-Speaker-v1.3.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="170">
   <si>
     <t>Comment</t>
   </si>
@@ -42,6 +42,9 @@
     <t>22uF</t>
   </si>
   <si>
+    <t>4.7nF</t>
+  </si>
+  <si>
     <t>PESD5V0H1BSFYL</t>
   </si>
   <si>
@@ -177,6 +180,9 @@
     <t>C23, C25, C26, C77</t>
   </si>
   <si>
+    <t>C79</t>
+  </si>
+  <si>
     <t>D1</t>
   </si>
   <si>
@@ -264,7 +270,7 @@
     <t>R30, R32, R35, R39</t>
   </si>
   <si>
-    <t>R65</t>
+    <t>R65, R69</t>
   </si>
   <si>
     <t>SW1</t>
@@ -309,6 +315,9 @@
     <t>Cap-0603</t>
   </si>
   <si>
+    <t>Cap-1206</t>
+  </si>
+  <si>
     <t>DSN0603-2</t>
   </si>
   <si>
@@ -405,6 +414,9 @@
     <t>C109447</t>
   </si>
   <si>
+    <t>C107198</t>
+  </si>
+  <si>
     <t>C477989</t>
   </si>
   <si>
@@ -517,9 +529,6 @@
   </si>
   <si>
     <t>C124375</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -975,7 +984,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -989,13 +998,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1003,13 +1012,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1017,13 +1026,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1031,13 +1040,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1045,13 +1054,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1059,13 +1068,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1073,13 +1082,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1087,13 +1096,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1101,13 +1110,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1115,13 +1124,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1129,13 +1138,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1143,13 +1152,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1157,13 +1166,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1171,13 +1180,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1185,41 +1194,41 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+      <c r="A16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
         <v>61300211121</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="B17" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>136</v>
+        <v>106</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1227,13 +1236,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1241,13 +1250,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1255,13 +1264,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1269,13 +1278,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1283,27 +1292,25 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>140</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="D22" s="4"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1311,13 +1318,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1325,13 +1332,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1339,13 +1346,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1353,13 +1360,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1367,13 +1374,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1381,13 +1388,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1395,13 +1402,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1409,13 +1416,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1423,13 +1430,13 @@
         <v>30</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1437,41 +1444,41 @@
         <v>31</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1479,13 +1486,13 @@
         <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1493,13 +1500,13 @@
         <v>34</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1507,13 +1514,13 @@
         <v>35</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1521,13 +1528,13 @@
         <v>36</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>36</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1535,27 +1542,25 @@
         <v>37</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>157</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D40" s="4"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1563,13 +1568,13 @@
         <v>39</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1577,41 +1582,41 @@
         <v>40</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>42</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1619,13 +1624,13 @@
         <v>43</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1633,13 +1638,27 @@
         <v>44</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>164</v>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
